--- a/3course/distributiveOperations/lab2/lab2.xlsx
+++ b/3course/distributiveOperations/lab2/lab2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\uni\3course\distributiveOperations\lab2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\University\3course\distributiveOperations\lab2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -131,7 +131,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -191,19 +191,6 @@
       <bottom style="thin">
         <color theme="0" tint="-0.24994659260841701"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -291,52 +278,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -346,96 +292,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -751,258 +667,244 @@
     <col min="16" max="16" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="H2" s="28" t="s">
+    <row r="2" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="H2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="K2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="21"/>
-    </row>
-    <row r="3" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C3" s="32" t="s">
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+    </row>
+    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="26" t="s">
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="26"/>
-      <c r="M3" s="27" t="s">
+      <c r="L3" s="16"/>
+      <c r="M3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="27"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="21"/>
-    </row>
-    <row r="4" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C4" s="11" t="s">
+      <c r="N3" s="17"/>
+    </row>
+    <row r="4" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="8" t="s">
+      <c r="H4" s="18"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="O4" s="23"/>
-      <c r="P4" s="20"/>
-    </row>
-    <row r="5" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C5" s="11">
+    </row>
+    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C5" s="7">
         <v>1</v>
       </c>
-      <c r="D5" s="12">
-        <v>10</v>
-      </c>
-      <c r="E5" s="13">
-        <v>5.0000000000000004E-6</v>
-      </c>
-      <c r="F5" s="14">
+      <c r="D5" s="8">
+        <v>12</v>
+      </c>
+      <c r="E5" s="9">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="F5" s="10">
         <f>D5*D5*(2*D5-1)*$E$17</f>
-        <v>5.3233054129154165E-6</v>
-      </c>
-      <c r="H5" s="9">
+        <v>9.2793618566188729E-6</v>
+      </c>
+      <c r="H5" s="14">
         <v>1</v>
       </c>
-      <c r="I5" s="11">
-        <v>10</v>
-      </c>
-      <c r="J5" s="14">
-        <v>5.0000000000000004E-6</v>
+      <c r="I5" s="15">
+        <v>12</v>
+      </c>
+      <c r="J5" s="3">
+        <v>7.9999999999999996E-6</v>
       </c>
       <c r="K5" s="2">
-        <v>8.7999999999999998E-5</v>
+        <v>1.8200000000000001E-4</v>
       </c>
       <c r="L5" s="3">
         <f>J5/K5</f>
-        <v>5.6818181818181823E-2</v>
+        <v>4.3956043956043953E-2</v>
       </c>
       <c r="M5" s="2">
-        <v>3.2699999999999998E-4</v>
+        <v>6.2699999999999995E-4</v>
       </c>
       <c r="N5" s="3">
         <f>J5/M5</f>
-        <v>1.5290519877675842E-2</v>
-      </c>
-      <c r="O5" s="25"/>
-      <c r="P5" s="18"/>
-    </row>
-    <row r="6" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="11">
+        <v>1.2759170653907496E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C6" s="7">
         <v>2</v>
       </c>
-      <c r="D6" s="12">
-        <v>100</v>
-      </c>
-      <c r="E6" s="13">
-        <v>4.3499999999999997E-3</v>
-      </c>
-      <c r="F6" s="14">
-        <f t="shared" ref="F5:F12" si="0">D6*D6*(2*D6-1)*$E$17</f>
-        <v>5.5754619851061463E-3</v>
-      </c>
-      <c r="H6" s="9">
+      <c r="D6" s="8">
+        <v>102</v>
+      </c>
+      <c r="E6" s="9">
+        <v>4.8719999999999996E-3</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" ref="F6:F12" si="0">D6*D6*(2*D6-1)*$E$17</f>
+        <v>5.917307848285429E-3</v>
+      </c>
+      <c r="H6" s="14">
         <v>2</v>
       </c>
-      <c r="I6" s="11">
-        <v>100</v>
-      </c>
-      <c r="J6" s="14">
-        <v>4.3499999999999997E-3</v>
+      <c r="I6" s="15">
+        <v>102</v>
+      </c>
+      <c r="J6" s="3">
+        <v>4.8719999999999996E-3</v>
       </c>
       <c r="K6" s="2">
-        <v>1.2539999999999999E-3</v>
+        <v>1.9170000000000001E-3</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" ref="L6:L12" si="1">J6/K6</f>
-        <v>3.4688995215311005</v>
+        <v>2.5414710485133019</v>
       </c>
       <c r="M6" s="2">
-        <v>1.3550000000000001E-3</v>
+        <v>1.4139999999999999E-3</v>
       </c>
       <c r="N6" s="3">
         <f t="shared" ref="N6:N12" si="2">J6/M6</f>
-        <v>3.2103321033210328</v>
-      </c>
-      <c r="O6" s="25"/>
-      <c r="P6" s="18"/>
-    </row>
-    <row r="7" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="11">
+        <v>3.4455445544554455</v>
+      </c>
+    </row>
+    <row r="7" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C7" s="7">
         <v>3</v>
       </c>
-      <c r="D7" s="12">
-        <v>500</v>
-      </c>
-      <c r="E7" s="13">
-        <v>0.39789799999999997</v>
-      </c>
-      <c r="F7" s="14">
+      <c r="D7" s="8">
+        <v>498</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.44658799999999998</v>
+      </c>
+      <c r="F7" s="10">
         <f t="shared" si="0"/>
-        <v>0.6997344878292765</v>
-      </c>
-      <c r="H7" s="9">
+        <v>0.69136843707713236</v>
+      </c>
+      <c r="H7" s="14">
         <v>3</v>
       </c>
-      <c r="I7" s="11">
-        <v>500</v>
-      </c>
-      <c r="J7" s="14">
-        <v>0.39789799999999997</v>
+      <c r="I7" s="15">
+        <v>498</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.44658799999999998</v>
       </c>
       <c r="K7" s="2">
-        <v>8.9525999999999994E-2</v>
+        <v>9.1414999999999996E-2</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="1"/>
-        <v>4.4444965708285862</v>
+        <v>4.8852814089591421</v>
       </c>
       <c r="M7" s="2">
-        <v>7.7677999999999997E-2</v>
+        <v>7.6951000000000006E-2</v>
       </c>
       <c r="N7" s="3">
         <f t="shared" si="2"/>
-        <v>5.1224027395144054</v>
-      </c>
-      <c r="O7" s="25"/>
-      <c r="P7" s="18"/>
-    </row>
-    <row r="8" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C8" s="11">
+        <v>5.8035373159543076</v>
+      </c>
+    </row>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C8" s="7">
         <v>4</v>
       </c>
-      <c r="D8" s="12">
-        <v>1000</v>
-      </c>
-      <c r="E8" s="13">
-        <v>4.199471</v>
-      </c>
-      <c r="F8" s="14">
+      <c r="D8" s="8">
+        <v>1002</v>
+      </c>
+      <c r="E8" s="9">
+        <v>7.2452680000000003</v>
+      </c>
+      <c r="F8" s="10">
         <f t="shared" si="0"/>
-        <v>5.6006776423252198</v>
-      </c>
-      <c r="H8" s="9">
+        <v>5.6343545870320133</v>
+      </c>
+      <c r="H8" s="14">
         <v>4</v>
       </c>
-      <c r="I8" s="11">
-        <v>1000</v>
-      </c>
-      <c r="J8" s="14">
-        <v>4.199471</v>
+      <c r="I8" s="15">
+        <v>1002</v>
+      </c>
+      <c r="J8" s="3">
+        <v>7.2452680000000003</v>
       </c>
       <c r="K8" s="2">
-        <v>0.93026200000000003</v>
+        <v>1.3534679999999999</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="1"/>
-        <v>4.5142884477706282</v>
+        <v>5.3531136310574023</v>
       </c>
       <c r="M8" s="2">
-        <v>0.70000700000000005</v>
+        <v>0.65709799999999996</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="2"/>
-        <v>5.9991842938713464</v>
-      </c>
-      <c r="O8" s="25"/>
-      <c r="P8" s="18"/>
-    </row>
-    <row r="9" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C9" s="11">
+        <v>11.026160481389383</v>
+      </c>
+    </row>
+    <row r="9" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C9" s="7">
         <v>5</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="8">
         <v>1500</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="9">
         <v>18.905439000000001</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="10">
         <f t="shared" si="0"/>
         <v>18.905439000000001</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="14">
         <v>5</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="15">
         <v>1500</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="3">
         <v>18.905439000000001</v>
       </c>
       <c r="K9" s="2">
@@ -1019,110 +921,104 @@
         <f t="shared" si="2"/>
         <v>6.9293334359605918</v>
       </c>
-      <c r="O9" s="25"/>
-      <c r="P9" s="18"/>
-    </row>
-    <row r="10" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C10" s="11">
+    </row>
+    <row r="10" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C10" s="7">
         <v>6</v>
       </c>
-      <c r="D10" s="12">
-        <v>2000</v>
-      </c>
-      <c r="E10" s="13">
-        <v>40.755063999999997</v>
-      </c>
-      <c r="F10" s="14">
+      <c r="D10" s="8">
+        <v>1998</v>
+      </c>
+      <c r="E10" s="9">
+        <v>62.412781000000003</v>
+      </c>
+      <c r="F10" s="10">
         <f t="shared" si="0"/>
-        <v>44.816628097365793</v>
-      </c>
-      <c r="H10" s="9">
+        <v>44.682301433585302</v>
+      </c>
+      <c r="H10" s="14">
         <v>6</v>
       </c>
-      <c r="I10" s="11">
-        <v>2000</v>
-      </c>
-      <c r="J10" s="14">
-        <v>40.755063999999997</v>
+      <c r="I10" s="15">
+        <v>1998</v>
+      </c>
+      <c r="J10" s="3">
+        <v>62.412781000000003</v>
       </c>
       <c r="K10" s="2">
-        <v>9.2633109999999999</v>
+        <v>21.280989000000002</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="1"/>
-        <v>4.3996216903437659</v>
+        <v>2.9327951346622094</v>
       </c>
       <c r="M10" s="2">
-        <v>12.917833999999999</v>
+        <v>10.823134</v>
       </c>
       <c r="N10" s="3">
         <f t="shared" si="2"/>
-        <v>3.154945635622814</v>
-      </c>
-      <c r="O10" s="25"/>
-      <c r="P10" s="18"/>
-    </row>
-    <row r="11" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C11" s="11">
+        <v>5.7666089138321679</v>
+      </c>
+    </row>
+    <row r="11" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C11" s="7">
         <v>7</v>
       </c>
-      <c r="D11" s="12">
-        <v>2500</v>
-      </c>
-      <c r="E11" s="13">
-        <v>102.93827899999999</v>
-      </c>
-      <c r="F11" s="14">
+      <c r="D11" s="8">
+        <v>2502</v>
+      </c>
+      <c r="E11" s="9">
+        <v>133.13329999999999</v>
+      </c>
+      <c r="F11" s="10">
         <f t="shared" si="0"/>
-        <v>87.536854470934756</v>
-      </c>
-      <c r="H11" s="9">
+        <v>87.74712506836579</v>
+      </c>
+      <c r="H11" s="14">
         <v>7</v>
       </c>
-      <c r="I11" s="11">
-        <v>2500</v>
-      </c>
-      <c r="J11" s="14">
-        <v>102.93827899999999</v>
+      <c r="I11" s="15">
+        <v>2502</v>
+      </c>
+      <c r="J11" s="3">
+        <v>133.13329999999999</v>
       </c>
       <c r="K11" s="2">
-        <v>31.069289000000001</v>
+        <v>42.305205000000001</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="1"/>
-        <v>3.3131842508529883</v>
+        <v>3.1469721042599836</v>
       </c>
       <c r="M11" s="2">
-        <v>26.527404000000001</v>
+        <v>21.291824999999999</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="2"/>
-        <v>3.8804505333428025</v>
-      </c>
-      <c r="O11" s="25"/>
-      <c r="P11" s="18"/>
-    </row>
-    <row r="12" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C12" s="11">
+        <v>6.2527895095887738</v>
+      </c>
+    </row>
+    <row r="12" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C12" s="7">
         <v>8</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="8">
         <v>3000</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="9">
         <v>163.98787300000001</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="10">
         <f t="shared" si="0"/>
         <v>151.26872765721907</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="14">
         <v>8</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="15">
         <v>3000</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="3">
         <v>163.98787300000001</v>
       </c>
       <c r="K12" s="2">
@@ -1139,216 +1035,137 @@
         <f t="shared" si="2"/>
         <v>6.2046456709388433</v>
       </c>
-      <c r="O12" s="25"/>
-      <c r="P12" s="18"/>
-    </row>
-    <row r="13" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-    </row>
-    <row r="14" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-    </row>
-    <row r="15" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C15" s="33" t="s">
+    </row>
+    <row r="13" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="34"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="36"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
-    </row>
-    <row r="16" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C16" s="30" t="s">
+      <c r="D15" s="24"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="26"/>
+    </row>
+    <row r="16" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C16" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="15">
+      <c r="D16" s="21"/>
+      <c r="E16" s="11">
         <f>1500*1500*(2*1500-1)</f>
         <v>6747750000</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
+      <c r="F16" s="4"/>
     </row>
     <row r="17" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="13">
         <f>E9/E16</f>
         <v>2.8017396910081139E-9</v>
       </c>
       <c r="F17" s="1"/>
     </row>
-    <row r="20" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-    </row>
-    <row r="21" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-    </row>
-    <row r="22" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J22" s="4"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J23" s="6"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-    </row>
-    <row r="24" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J24" s="6"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-    </row>
     <row r="25" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J25" s="6"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
     </row>
     <row r="26" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J26" s="6"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
     </row>
     <row r="27" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J27" s="6"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
     </row>
     <row r="28" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J28" s="6"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
     </row>
     <row r="29" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J29" s="6"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
     </row>
     <row r="30" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J30" s="6"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
     </row>
     <row r="31" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J31" s="6"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
     </row>
     <row r="32" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="J32" s="6"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
     </row>
     <row r="33" spans="10:16" x14ac:dyDescent="0.3">
-      <c r="J33" s="6"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
     </row>
     <row r="34" spans="10:16" x14ac:dyDescent="0.3">
-      <c r="J34" s="6"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="9">
